--- a/rapporten/prijsrapport-NL-2026-05-17.xlsx
+++ b/rapporten/prijsrapport-NL-2026-05-17.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="155">
   <si>
     <t>Product</t>
   </si>
@@ -124,81 +124,45 @@
     <t>Dorsh</t>
   </si>
   <si>
-    <t>Hello Kitty Giftset 3 x 15ml Eau de Parfum</t>
-  </si>
-  <si>
-    <t>7640158817032</t>
+    <t>Azira - Dream Oasis - Eau de Parfum Unisex</t>
+  </si>
+  <si>
+    <t>8721349102706</t>
+  </si>
+  <si>
+    <t>Creation Lamis Overdrive Eau de Parfum 100ml</t>
+  </si>
+  <si>
+    <t>6291012000261</t>
+  </si>
+  <si>
+    <t>NG Dark Elixir Men Eau de Toilette 100 ml</t>
+  </si>
+  <si>
+    <t>8719214757229</t>
+  </si>
+  <si>
+    <t>Omerta Love Feathers - Eau de parfum - 100ML</t>
+  </si>
+  <si>
+    <t>8715658999430</t>
+  </si>
+  <si>
+    <t>Omerta - Pink Shoe - Eau de Parfum 100ml</t>
+  </si>
+  <si>
+    <t>8715658380931</t>
+  </si>
+  <si>
+    <t>Creation Lamis Paraverse 100ml Eau de Parfum for women</t>
+  </si>
+  <si>
+    <t>6291012005082</t>
   </si>
   <si>
     <t>Koopjesfun.nl</t>
   </si>
   <si>
-    <t>NG Dark Elixir Men Eau de Toilette 100 ml</t>
-  </si>
-  <si>
-    <t>8719214757229</t>
-  </si>
-  <si>
-    <t>Azira - Dream Oasis - Eau de Parfum Unisex</t>
-  </si>
-  <si>
-    <t>8721349102706</t>
-  </si>
-  <si>
-    <t>Creation Lamis Overdrive Eau de Parfum 100ml</t>
-  </si>
-  <si>
-    <t>6291012000261</t>
-  </si>
-  <si>
-    <t>Omerta La Donna X Eau De Parfum voor haar 100ML</t>
-  </si>
-  <si>
-    <t>5145200059016</t>
-  </si>
-  <si>
-    <t>Sentio What Happens Under The Mistletoe Stays Under The Mistletoe - Eau de parfum</t>
-  </si>
-  <si>
-    <t>8721055492795</t>
-  </si>
-  <si>
-    <t>Bubble Bliss Giftset Like a Fairytale-Eau de Parfum</t>
-  </si>
-  <si>
-    <t>8721055494287</t>
-  </si>
-  <si>
-    <t>Sentio Happy Birthday Giftset - Luxe parfum en showergel voor iedereen</t>
-  </si>
-  <si>
-    <t>8721055494140</t>
-  </si>
-  <si>
-    <t>Hello Kitty - Giftset - Unicorn Cloud - Showergel + Water-Based Parfum - Cadeauset voor Kinderen - Geschenkset</t>
-  </si>
-  <si>
-    <t>7640158816974</t>
-  </si>
-  <si>
-    <t>Creation Lamis Diva Essence Eau de Parfum For Women 100ml</t>
-  </si>
-  <si>
-    <t>6291012005662</t>
-  </si>
-  <si>
-    <t>Omerta Love Feathers - Eau de parfum - 100ML</t>
-  </si>
-  <si>
-    <t>8715658999430</t>
-  </si>
-  <si>
-    <t>Omerta - Pink Shoe - Eau de Parfum 100ml</t>
-  </si>
-  <si>
-    <t>8715658380931</t>
-  </si>
-  <si>
     <t>Omerta - Big Release The Mood - EDT men - 100ml</t>
   </si>
   <si>
@@ -325,28 +289,10 @@
     <t>8715658380580</t>
   </si>
   <si>
-    <t>Omerta - Conclude Oud Orient Perfection - Eau De Parfum - 100ML</t>
-  </si>
-  <si>
-    <t>8715658370550</t>
-  </si>
-  <si>
-    <t>Street Looks - Wild Challenge - Eau De Toilette - 100ML</t>
-  </si>
-  <si>
-    <t>8715658330004</t>
-  </si>
-  <si>
-    <t>Real Time - Night Blue Mission Pour Homme - Eau De Toilette - 100ML</t>
-  </si>
-  <si>
-    <t>8715658002772</t>
-  </si>
-  <si>
-    <t>Creation Lamis Diable Bleu parfum - Oriëntaalse en houtige eau de parfum voor dames</t>
-  </si>
-  <si>
-    <t>5414666001366</t>
+    <t>Hello Kitty - Giftset - Sweet Leopard Pink - Eau de Parfum + Bodymist - Cadeauset voor Kinderen - Geschenkset</t>
+  </si>
+  <si>
+    <t>8721055496373</t>
   </si>
   <si>
     <t>Bubble Bliss - Unicorn Sprinkles - Discover - Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
@@ -364,18 +310,6 @@
     <t>8721055494225</t>
   </si>
   <si>
-    <t>Linn Young "Je Suis Sure Et Certaine" Eau de parfum 100ml</t>
-  </si>
-  <si>
-    <t>8715658400295</t>
-  </si>
-  <si>
-    <t>Real Time - Out Of Order - Eau De Toilette - 100ML</t>
-  </si>
-  <si>
-    <t>8715658350033</t>
-  </si>
-  <si>
     <t>Bubble Bliss - Like a Fairytale - Glimmering Grace - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
   </si>
   <si>
@@ -454,12 +388,6 @@
     <t>8721055493884</t>
   </si>
   <si>
-    <t>Hello Kitty - Giftset - Kisses - Showergel + Eau de Parfum - Cadeauset voor Kinderen - Geschenkset</t>
-  </si>
-  <si>
-    <t>8721055493440</t>
-  </si>
-  <si>
     <t>Hello Kitty-Spring Time-15ml Eau de Parfum</t>
   </si>
   <si>
@@ -496,10 +424,10 @@
     <t>8721055493228</t>
   </si>
   <si>
-    <t>NG Heavens Body 100ML Dames Eau de Parfum</t>
-  </si>
-  <si>
-    <t>8719214751920</t>
+    <t>Vibezz-French Marine-Eau de Toilette For Him-100ml</t>
+  </si>
+  <si>
+    <t>7640158819234</t>
   </si>
   <si>
     <t>Real Time - Please Call Me - Eau de parfum - 100ML</t>
@@ -508,133 +436,46 @@
     <t>8715658360971</t>
   </si>
   <si>
-    <t>NG Classic Men Eau de Toilette Spray 100 ml</t>
-  </si>
-  <si>
-    <t>8719214751203</t>
-  </si>
-  <si>
-    <t>SENTIO FEESTDAGEN PINK - Family Magical - Eau de Parfum 50ml</t>
-  </si>
-  <si>
-    <t>8721055492740</t>
-  </si>
-  <si>
-    <t>SENTIO FEESTDAGEN PINK - Happy Holidays - Body Mist 250ml</t>
-  </si>
-  <si>
-    <t>8721055493082</t>
-  </si>
-  <si>
-    <t>Omerta - Red Class Elixir de Luxe - Eau De Parfum - 100ML</t>
-  </si>
-  <si>
-    <t>8715658370574</t>
-  </si>
-  <si>
-    <t>Omerta - Express sensualite Captive - Eau De Toilette - 100ML</t>
-  </si>
-  <si>
-    <t>8715658999027</t>
-  </si>
-  <si>
-    <t>Bubble Bliss Flamingo Giftbook Parfum Pink &amp; Proud EDP voor meisjes 50ml</t>
-  </si>
-  <si>
-    <t>8721055492184</t>
-  </si>
-  <si>
-    <t>Real Time Queen of Space parfum - Eau de parfum voor elegante vrouwen - 100ml</t>
-  </si>
-  <si>
-    <t>8715658360896</t>
-  </si>
-  <si>
-    <t>Real Time - Nuit Charmante - Eau de parfum - 100ML</t>
-  </si>
-  <si>
-    <t>8715658360001</t>
-  </si>
-  <si>
-    <t>Omerta - Couture Cat - Eau De Parfum - 100ML</t>
-  </si>
-  <si>
-    <t>8715658997733</t>
-  </si>
-  <si>
-    <t>Hello Kitty Choose Your Style Parfum set 6 stuks voor kinderen - 6x15ml - Meisjes</t>
-  </si>
-  <si>
-    <t>7640158816943</t>
-  </si>
-  <si>
-    <t>Vibezz-Confermato-Eau de Parfum For Her-100ml</t>
-  </si>
-  <si>
-    <t>7640158819197</t>
-  </si>
-  <si>
-    <t>SmileShop.NL</t>
-  </si>
-  <si>
-    <t>Creation Lamis Fatal Snake Magical Giftset</t>
-  </si>
-  <si>
-    <t>6291012871731</t>
-  </si>
-  <si>
-    <t>Bubble Bliss Fantastic Flamingo - Parfum Set Van 6 Stuks - Eau de Parfum Voor Kinderen - 6x15ml</t>
-  </si>
-  <si>
-    <t>8721055493914</t>
-  </si>
-  <si>
-    <t>Real Time Mise Eau de Toilette100ml</t>
-  </si>
-  <si>
-    <t>8715658009733</t>
-  </si>
-  <si>
-    <t>Real Time Love You Red 100 ml - Eau de Parfum - Damesparfum</t>
-  </si>
-  <si>
-    <t>8715658360056</t>
-  </si>
-  <si>
-    <t>Street Looks Uptown Babe eau de parfum 100ml</t>
-  </si>
-  <si>
-    <t>8715658340270</t>
-  </si>
-  <si>
-    <t>Omerta Oh My Dear L'extase parfum - Eau de parfum - 100ML</t>
-  </si>
-  <si>
-    <t>8715658380245</t>
-  </si>
-  <si>
-    <t>Creation Lamis Golden Wave for Men Giftset</t>
-  </si>
-  <si>
-    <t>6291012002661</t>
-  </si>
-  <si>
-    <t>Next Generation Classic Woman Elegance Eau de Parfum 100ml</t>
-  </si>
-  <si>
-    <t>8719214753269</t>
-  </si>
-  <si>
-    <t>Real Time - Black Warrior - Eau De Parfum - 100Ml</t>
-  </si>
-  <si>
-    <t>8715658009566</t>
-  </si>
-  <si>
-    <t>Real Time - Legendary Life For Men - Eau de toilette - 100ML</t>
-  </si>
-  <si>
-    <t>8715658350453</t>
+    <t>Omerta - Candy Puff - Eau de parfum - 100ML</t>
+  </si>
+  <si>
+    <t>8715658380801</t>
+  </si>
+  <si>
+    <t>Vibezz Astrolux parfum - Eau de parfum voor haar - 100ml</t>
+  </si>
+  <si>
+    <t>7640158819173</t>
+  </si>
+  <si>
+    <t>Real Time - Smart Lady For Women - Eau de parfum - 100ML</t>
+  </si>
+  <si>
+    <t>8715658360995</t>
+  </si>
+  <si>
+    <t>SENTIO FEESTDAGEN PINK - Holly Jolly Magic - Eau de Parfum 50ml</t>
+  </si>
+  <si>
+    <t>8721055492719</t>
+  </si>
+  <si>
+    <t>Hello Kitty Delicate Flower Eau de Parfum voor Kinderen 50ml</t>
+  </si>
+  <si>
+    <t>7640158816875</t>
+  </si>
+  <si>
+    <t>Real Time Loveliness La Passione - Eau de parfum - 100ML</t>
+  </si>
+  <si>
+    <t>8715658360759</t>
+  </si>
+  <si>
+    <t>Hello Kitty - Giftset - Delicate Flower - Showergel + Eau de Parfum - Cadeauset voor Kinderen - Geschenkset</t>
+  </si>
+  <si>
+    <t>7640158816950</t>
   </si>
 </sst>
 </file>
@@ -1026,7 +867,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H97"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -1385,19 +1226,19 @@
         <v>38</v>
       </c>
       <c r="C14" s="1">
-        <v>15.19</v>
+        <v>14.25</v>
       </c>
       <c r="D14" s="1">
-        <v>14.8</v>
+        <v>13.91</v>
       </c>
       <c r="E14" s="1">
-        <v>0.39</v>
+        <v>0.34</v>
       </c>
       <c r="F14" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G14" s="1">
-        <v>14.8</v>
+        <v>13.91</v>
       </c>
       <c r="H14" t="s">
         <v>11</v>
@@ -1405,25 +1246,25 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" t="s">
         <v>40</v>
-      </c>
-      <c r="B15" t="s">
-        <v>41</v>
       </c>
       <c r="C15" s="1">
         <v>9.79</v>
       </c>
       <c r="D15" s="1">
-        <v>9.42</v>
+        <v>9.45</v>
       </c>
       <c r="E15" s="1">
-        <v>0.37</v>
+        <v>0.34</v>
       </c>
       <c r="F15" t="s">
         <v>36</v>
       </c>
       <c r="G15" s="1">
-        <v>9.42</v>
+        <v>9.45</v>
       </c>
       <c r="H15" t="s">
         <v>11</v>
@@ -1431,25 +1272,25 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" t="s">
         <v>42</v>
       </c>
-      <c r="B16" t="s">
-        <v>43</v>
-      </c>
       <c r="C16" s="1">
-        <v>14.25</v>
+        <v>9.79</v>
       </c>
       <c r="D16" s="1">
-        <v>13.91</v>
+        <v>9.47</v>
       </c>
       <c r="E16" s="1">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="F16" t="s">
         <v>36</v>
       </c>
       <c r="G16" s="1">
-        <v>13.91</v>
+        <v>9.47</v>
       </c>
       <c r="H16" t="s">
         <v>11</v>
@@ -1457,25 +1298,25 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" t="s">
         <v>44</v>
-      </c>
-      <c r="B17" t="s">
-        <v>45</v>
       </c>
       <c r="C17" s="1">
         <v>9.79</v>
       </c>
       <c r="D17" s="1">
-        <v>9.45</v>
+        <v>9.5</v>
       </c>
       <c r="E17" s="1">
-        <v>0.34</v>
+        <v>0.29</v>
       </c>
       <c r="F17" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="G17" s="1">
-        <v>9.45</v>
+        <v>9.5</v>
       </c>
       <c r="H17" t="s">
         <v>11</v>
@@ -1483,25 +1324,25 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" t="s">
         <v>46</v>
       </c>
-      <c r="B18" t="s">
-        <v>47</v>
-      </c>
       <c r="C18" s="1">
-        <v>14.59</v>
+        <v>9.79</v>
       </c>
       <c r="D18" s="1">
-        <v>14.26</v>
+        <v>9.5</v>
       </c>
       <c r="E18" s="1">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="F18" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="G18" s="1">
-        <v>14.26</v>
+        <v>9.5</v>
       </c>
       <c r="H18" t="s">
         <v>11</v>
@@ -1509,25 +1350,25 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" t="s">
         <v>48</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" s="1">
+        <v>14.39</v>
+      </c>
+      <c r="D19" s="1">
+        <v>14.1</v>
+      </c>
+      <c r="E19" s="1">
+        <v>0.29</v>
+      </c>
+      <c r="F19" t="s">
         <v>49</v>
       </c>
-      <c r="C19" s="1">
-        <v>8.25</v>
-      </c>
-      <c r="D19" s="1">
-        <v>7.92</v>
-      </c>
-      <c r="E19" s="1">
-        <v>0.33</v>
-      </c>
-      <c r="F19" t="s">
-        <v>36</v>
-      </c>
       <c r="G19" s="1">
-        <v>7.92</v>
+        <v>14.1</v>
       </c>
       <c r="H19" t="s">
         <v>11</v>
@@ -1541,19 +1382,19 @@
         <v>51</v>
       </c>
       <c r="C20" s="1">
-        <v>14.59</v>
+        <v>9.79</v>
       </c>
       <c r="D20" s="1">
-        <v>14.26</v>
+        <v>9.5</v>
       </c>
       <c r="E20" s="1">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="F20" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="G20" s="1">
-        <v>14.26</v>
+        <v>9.5</v>
       </c>
       <c r="H20" t="s">
         <v>11</v>
@@ -1567,19 +1408,19 @@
         <v>53</v>
       </c>
       <c r="C21" s="1">
-        <v>14.59</v>
+        <v>9.79</v>
       </c>
       <c r="D21" s="1">
-        <v>14.28</v>
+        <v>9.5</v>
       </c>
       <c r="E21" s="1">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="F21" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="G21" s="1">
-        <v>14.28</v>
+        <v>9.5</v>
       </c>
       <c r="H21" t="s">
         <v>11</v>
@@ -1593,19 +1434,19 @@
         <v>55</v>
       </c>
       <c r="C22" s="1">
-        <v>14.58</v>
+        <v>9.79</v>
       </c>
       <c r="D22" s="1">
-        <v>14.27</v>
+        <v>9.5</v>
       </c>
       <c r="E22" s="1">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="F22" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="G22" s="1">
-        <v>14.27</v>
+        <v>9.5</v>
       </c>
       <c r="H22" t="s">
         <v>11</v>
@@ -1619,19 +1460,19 @@
         <v>57</v>
       </c>
       <c r="C23" s="1">
-        <v>14.58</v>
+        <v>9.79</v>
       </c>
       <c r="D23" s="1">
-        <v>14.27</v>
+        <v>9.5</v>
       </c>
       <c r="E23" s="1">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="F23" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="G23" s="1">
-        <v>14.27</v>
+        <v>9.5</v>
       </c>
       <c r="H23" t="s">
         <v>11</v>
@@ -2087,19 +1928,19 @@
         <v>93</v>
       </c>
       <c r="C41" s="1">
-        <v>9.79</v>
+        <v>14.19</v>
       </c>
       <c r="D41" s="1">
-        <v>9.5</v>
+        <v>13.91</v>
       </c>
       <c r="E41" s="1">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="F41" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="G41" s="1">
-        <v>9.5</v>
+        <v>13.91</v>
       </c>
       <c r="H41" t="s">
         <v>11</v>
@@ -2113,19 +1954,19 @@
         <v>95</v>
       </c>
       <c r="C42" s="1">
-        <v>9.79</v>
+        <v>5.25</v>
       </c>
       <c r="D42" s="1">
-        <v>9.5</v>
+        <v>4.99</v>
       </c>
       <c r="E42" s="1">
-        <v>0.29</v>
+        <v>0.26</v>
       </c>
       <c r="F42" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="G42" s="1">
-        <v>9.5</v>
+        <v>4.99</v>
       </c>
       <c r="H42" t="s">
         <v>11</v>
@@ -2133,25 +1974,25 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>97</v>
+      </c>
+      <c r="B43" t="s">
+        <v>98</v>
+      </c>
+      <c r="C43" s="1">
+        <v>5.25</v>
+      </c>
+      <c r="D43" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="E43" s="1">
+        <v>0.26</v>
+      </c>
+      <c r="F43" t="s">
         <v>96</v>
       </c>
-      <c r="B43" t="s">
-        <v>97</v>
-      </c>
-      <c r="C43" s="1">
-        <v>9.79</v>
-      </c>
-      <c r="D43" s="1">
-        <v>9.5</v>
-      </c>
-      <c r="E43" s="1">
-        <v>0.29</v>
-      </c>
-      <c r="F43" t="s">
-        <v>16</v>
-      </c>
       <c r="G43" s="1">
-        <v>9.5</v>
+        <v>4.99</v>
       </c>
       <c r="H43" t="s">
         <v>11</v>
@@ -2159,25 +2000,25 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B44" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C44" s="1">
-        <v>9.79</v>
+        <v>5.25</v>
       </c>
       <c r="D44" s="1">
-        <v>9.5</v>
+        <v>4.99</v>
       </c>
       <c r="E44" s="1">
-        <v>0.29</v>
+        <v>0.26</v>
       </c>
       <c r="F44" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="G44" s="1">
-        <v>9.5</v>
+        <v>4.99</v>
       </c>
       <c r="H44" t="s">
         <v>11</v>
@@ -2185,25 +2026,25 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B45" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C45" s="1">
-        <v>9.79</v>
+        <v>5.25</v>
       </c>
       <c r="D45" s="1">
-        <v>9.5</v>
+        <v>4.99</v>
       </c>
       <c r="E45" s="1">
-        <v>0.29</v>
+        <v>0.26</v>
       </c>
       <c r="F45" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="G45" s="1">
-        <v>9.5</v>
+        <v>4.99</v>
       </c>
       <c r="H45" t="s">
         <v>11</v>
@@ -2211,25 +2052,25 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B46" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C46" s="1">
-        <v>9.79</v>
+        <v>5.25</v>
       </c>
       <c r="D46" s="1">
-        <v>9.5</v>
+        <v>4.99</v>
       </c>
       <c r="E46" s="1">
-        <v>0.29</v>
+        <v>0.26</v>
       </c>
       <c r="F46" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="G46" s="1">
-        <v>9.5</v>
+        <v>4.99</v>
       </c>
       <c r="H46" t="s">
         <v>11</v>
@@ -2237,25 +2078,25 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B47" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C47" s="1">
-        <v>13.95</v>
+        <v>5.25</v>
       </c>
       <c r="D47" s="1">
-        <v>13.68</v>
+        <v>4.99</v>
       </c>
       <c r="E47" s="1">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="F47" t="s">
-        <v>39</v>
+        <v>96</v>
       </c>
       <c r="G47" s="1">
-        <v>13.68</v>
+        <v>4.99</v>
       </c>
       <c r="H47" t="s">
         <v>11</v>
@@ -2263,25 +2104,25 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B48" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C48" s="1">
-        <v>13.95</v>
+        <v>5.25</v>
       </c>
       <c r="D48" s="1">
-        <v>13.68</v>
+        <v>4.99</v>
       </c>
       <c r="E48" s="1">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="F48" t="s">
-        <v>39</v>
+        <v>96</v>
       </c>
       <c r="G48" s="1">
-        <v>13.68</v>
+        <v>4.99</v>
       </c>
       <c r="H48" t="s">
         <v>11</v>
@@ -2289,25 +2130,25 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B49" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C49" s="1">
-        <v>13.95</v>
+        <v>5.25</v>
       </c>
       <c r="D49" s="1">
-        <v>13.68</v>
+        <v>4.99</v>
       </c>
       <c r="E49" s="1">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="F49" t="s">
-        <v>39</v>
+        <v>96</v>
       </c>
       <c r="G49" s="1">
-        <v>13.68</v>
+        <v>4.99</v>
       </c>
       <c r="H49" t="s">
         <v>11</v>
@@ -2315,25 +2156,25 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B50" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C50" s="1">
-        <v>13.95</v>
+        <v>5.25</v>
       </c>
       <c r="D50" s="1">
-        <v>13.68</v>
+        <v>4.99</v>
       </c>
       <c r="E50" s="1">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="F50" t="s">
-        <v>39</v>
+        <v>96</v>
       </c>
       <c r="G50" s="1">
-        <v>13.68</v>
+        <v>4.99</v>
       </c>
       <c r="H50" t="s">
         <v>11</v>
@@ -2341,10 +2182,10 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B51" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C51" s="1">
         <v>5.25</v>
@@ -2356,7 +2197,7 @@
         <v>0.26</v>
       </c>
       <c r="F51" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="G51" s="1">
         <v>4.99</v>
@@ -2382,7 +2223,7 @@
         <v>0.26</v>
       </c>
       <c r="F52" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="G52" s="1">
         <v>4.99</v>
@@ -2399,19 +2240,19 @@
         <v>118</v>
       </c>
       <c r="C53" s="1">
-        <v>13.95</v>
+        <v>5.25</v>
       </c>
       <c r="D53" s="1">
-        <v>13.69</v>
+        <v>4.99</v>
       </c>
       <c r="E53" s="1">
         <v>0.26</v>
       </c>
       <c r="F53" t="s">
-        <v>39</v>
+        <v>96</v>
       </c>
       <c r="G53" s="1">
-        <v>13.69</v>
+        <v>4.99</v>
       </c>
       <c r="H53" t="s">
         <v>11</v>
@@ -2425,19 +2266,19 @@
         <v>120</v>
       </c>
       <c r="C54" s="1">
-        <v>13.95</v>
+        <v>5.25</v>
       </c>
       <c r="D54" s="1">
-        <v>13.69</v>
+        <v>4.99</v>
       </c>
       <c r="E54" s="1">
         <v>0.26</v>
       </c>
       <c r="F54" t="s">
-        <v>39</v>
+        <v>96</v>
       </c>
       <c r="G54" s="1">
-        <v>13.69</v>
+        <v>4.99</v>
       </c>
       <c r="H54" t="s">
         <v>11</v>
@@ -2460,7 +2301,7 @@
         <v>0.26</v>
       </c>
       <c r="F55" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="G55" s="1">
         <v>4.99</v>
@@ -2486,7 +2327,7 @@
         <v>0.26</v>
       </c>
       <c r="F56" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="G56" s="1">
         <v>4.99</v>
@@ -2512,7 +2353,7 @@
         <v>0.26</v>
       </c>
       <c r="F57" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="G57" s="1">
         <v>4.99</v>
@@ -2538,7 +2379,7 @@
         <v>0.26</v>
       </c>
       <c r="F58" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="G58" s="1">
         <v>4.99</v>
@@ -2564,7 +2405,7 @@
         <v>0.26</v>
       </c>
       <c r="F59" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="G59" s="1">
         <v>4.99</v>
@@ -2590,7 +2431,7 @@
         <v>0.26</v>
       </c>
       <c r="F60" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="G60" s="1">
         <v>4.99</v>
@@ -2616,7 +2457,7 @@
         <v>0.26</v>
       </c>
       <c r="F61" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="G61" s="1">
         <v>4.99</v>
@@ -2642,7 +2483,7 @@
         <v>0.26</v>
       </c>
       <c r="F62" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="G62" s="1">
         <v>4.99</v>
@@ -2659,19 +2500,19 @@
         <v>138</v>
       </c>
       <c r="C63" s="1">
-        <v>5.25</v>
+        <v>13.86</v>
       </c>
       <c r="D63" s="1">
-        <v>4.99</v>
+        <v>13.62</v>
       </c>
       <c r="E63" s="1">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="F63" t="s">
-        <v>114</v>
+        <v>49</v>
       </c>
       <c r="G63" s="1">
-        <v>4.99</v>
+        <v>13.62</v>
       </c>
       <c r="H63" t="s">
         <v>11</v>
@@ -2685,19 +2526,19 @@
         <v>140</v>
       </c>
       <c r="C64" s="1">
-        <v>5.25</v>
+        <v>13.89</v>
       </c>
       <c r="D64" s="1">
-        <v>4.99</v>
+        <v>13.65</v>
       </c>
       <c r="E64" s="1">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="F64" t="s">
-        <v>114</v>
+        <v>49</v>
       </c>
       <c r="G64" s="1">
-        <v>4.99</v>
+        <v>13.65</v>
       </c>
       <c r="H64" t="s">
         <v>11</v>
@@ -2711,19 +2552,19 @@
         <v>142</v>
       </c>
       <c r="C65" s="1">
-        <v>5.25</v>
+        <v>13.78</v>
       </c>
       <c r="D65" s="1">
-        <v>4.99</v>
+        <v>13.55</v>
       </c>
       <c r="E65" s="1">
-        <v>0.26</v>
+        <v>0.23</v>
       </c>
       <c r="F65" t="s">
-        <v>114</v>
+        <v>49</v>
       </c>
       <c r="G65" s="1">
-        <v>4.99</v>
+        <v>13.55</v>
       </c>
       <c r="H65" t="s">
         <v>11</v>
@@ -2737,19 +2578,19 @@
         <v>144</v>
       </c>
       <c r="C66" s="1">
-        <v>5.25</v>
+        <v>13.82</v>
       </c>
       <c r="D66" s="1">
-        <v>4.99</v>
+        <v>13.59</v>
       </c>
       <c r="E66" s="1">
-        <v>0.26</v>
+        <v>0.23</v>
       </c>
       <c r="F66" t="s">
-        <v>114</v>
+        <v>49</v>
       </c>
       <c r="G66" s="1">
-        <v>4.99</v>
+        <v>13.59</v>
       </c>
       <c r="H66" t="s">
         <v>11</v>
@@ -2763,19 +2604,19 @@
         <v>146</v>
       </c>
       <c r="C67" s="1">
-        <v>5.25</v>
+        <v>13.78</v>
       </c>
       <c r="D67" s="1">
-        <v>4.99</v>
+        <v>13.55</v>
       </c>
       <c r="E67" s="1">
-        <v>0.26</v>
+        <v>0.23</v>
       </c>
       <c r="F67" t="s">
-        <v>114</v>
+        <v>49</v>
       </c>
       <c r="G67" s="1">
-        <v>4.99</v>
+        <v>13.55</v>
       </c>
       <c r="H67" t="s">
         <v>11</v>
@@ -2789,19 +2630,19 @@
         <v>148</v>
       </c>
       <c r="C68" s="1">
-        <v>13.99</v>
+        <v>13.75</v>
       </c>
       <c r="D68" s="1">
-        <v>13.73</v>
+        <v>13.52</v>
       </c>
       <c r="E68" s="1">
-        <v>0.26</v>
+        <v>0.23</v>
       </c>
       <c r="F68" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="G68" s="1">
-        <v>13.73</v>
+        <v>13.52</v>
       </c>
       <c r="H68" t="s">
         <v>11</v>
@@ -2815,19 +2656,19 @@
         <v>150</v>
       </c>
       <c r="C69" s="1">
-        <v>5.25</v>
+        <v>12.87</v>
       </c>
       <c r="D69" s="1">
-        <v>4.99</v>
+        <v>12.73</v>
       </c>
       <c r="E69" s="1">
-        <v>0.26</v>
+        <v>0.14</v>
       </c>
       <c r="F69" t="s">
-        <v>114</v>
+        <v>49</v>
       </c>
       <c r="G69" s="1">
-        <v>4.99</v>
+        <v>12.73</v>
       </c>
       <c r="H69" t="s">
         <v>11</v>
@@ -2841,19 +2682,19 @@
         <v>152</v>
       </c>
       <c r="C70" s="1">
-        <v>5.25</v>
+        <v>12.35</v>
       </c>
       <c r="D70" s="1">
-        <v>4.99</v>
+        <v>12.26</v>
       </c>
       <c r="E70" s="1">
-        <v>0.26</v>
+        <v>0.09</v>
       </c>
       <c r="F70" t="s">
-        <v>114</v>
+        <v>49</v>
       </c>
       <c r="G70" s="1">
-        <v>4.99</v>
+        <v>12.26</v>
       </c>
       <c r="H70" t="s">
         <v>11</v>
@@ -2867,697 +2708,21 @@
         <v>154</v>
       </c>
       <c r="C71" s="1">
-        <v>5.25</v>
+        <v>12.45</v>
       </c>
       <c r="D71" s="1">
-        <v>4.99</v>
+        <v>12.36</v>
       </c>
       <c r="E71" s="1">
-        <v>0.26</v>
+        <v>0.09</v>
       </c>
       <c r="F71" t="s">
-        <v>114</v>
+        <v>49</v>
       </c>
       <c r="G71" s="1">
-        <v>4.99</v>
+        <v>12.36</v>
       </c>
       <c r="H71" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>155</v>
-      </c>
-      <c r="B72" t="s">
-        <v>156</v>
-      </c>
-      <c r="C72" s="1">
-        <v>5.25</v>
-      </c>
-      <c r="D72" s="1">
-        <v>4.99</v>
-      </c>
-      <c r="E72" s="1">
-        <v>0.26</v>
-      </c>
-      <c r="F72" t="s">
-        <v>114</v>
-      </c>
-      <c r="G72" s="1">
-        <v>4.99</v>
-      </c>
-      <c r="H72" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>157</v>
-      </c>
-      <c r="B73" t="s">
-        <v>158</v>
-      </c>
-      <c r="C73" s="1">
-        <v>5.25</v>
-      </c>
-      <c r="D73" s="1">
-        <v>4.99</v>
-      </c>
-      <c r="E73" s="1">
-        <v>0.26</v>
-      </c>
-      <c r="F73" t="s">
-        <v>114</v>
-      </c>
-      <c r="G73" s="1">
-        <v>4.99</v>
-      </c>
-      <c r="H73" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>159</v>
-      </c>
-      <c r="B74" t="s">
-        <v>160</v>
-      </c>
-      <c r="C74" s="1">
-        <v>5.25</v>
-      </c>
-      <c r="D74" s="1">
-        <v>4.99</v>
-      </c>
-      <c r="E74" s="1">
-        <v>0.26</v>
-      </c>
-      <c r="F74" t="s">
-        <v>114</v>
-      </c>
-      <c r="G74" s="1">
-        <v>4.99</v>
-      </c>
-      <c r="H74" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>161</v>
-      </c>
-      <c r="B75" t="s">
-        <v>162</v>
-      </c>
-      <c r="C75" s="1">
-        <v>12.5</v>
-      </c>
-      <c r="D75" s="1">
-        <v>12.26</v>
-      </c>
-      <c r="E75" s="1">
-        <v>0.24</v>
-      </c>
-      <c r="F75" t="s">
-        <v>39</v>
-      </c>
-      <c r="G75" s="1">
-        <v>12.26</v>
-      </c>
-      <c r="H75" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>163</v>
-      </c>
-      <c r="B76" t="s">
-        <v>164</v>
-      </c>
-      <c r="C76" s="1">
-        <v>13.89</v>
-      </c>
-      <c r="D76" s="1">
-        <v>13.65</v>
-      </c>
-      <c r="E76" s="1">
-        <v>0.24</v>
-      </c>
-      <c r="F76" t="s">
-        <v>39</v>
-      </c>
-      <c r="G76" s="1">
-        <v>13.65</v>
-      </c>
-      <c r="H76" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>165</v>
-      </c>
-      <c r="B77" t="s">
-        <v>166</v>
-      </c>
-      <c r="C77" s="1">
-        <v>12.5</v>
-      </c>
-      <c r="D77" s="1">
-        <v>12.27</v>
-      </c>
-      <c r="E77" s="1">
-        <v>0.23</v>
-      </c>
-      <c r="F77" t="s">
-        <v>39</v>
-      </c>
-      <c r="G77" s="1">
-        <v>12.27</v>
-      </c>
-      <c r="H77" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>167</v>
-      </c>
-      <c r="B78" t="s">
-        <v>168</v>
-      </c>
-      <c r="C78" s="1">
-        <v>13.75</v>
-      </c>
-      <c r="D78" s="1">
-        <v>13.52</v>
-      </c>
-      <c r="E78" s="1">
-        <v>0.23</v>
-      </c>
-      <c r="F78" t="s">
-        <v>39</v>
-      </c>
-      <c r="G78" s="1">
-        <v>13.52</v>
-      </c>
-      <c r="H78" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>169</v>
-      </c>
-      <c r="B79" t="s">
-        <v>170</v>
-      </c>
-      <c r="C79" s="1">
-        <v>13.82</v>
-      </c>
-      <c r="D79" s="1">
-        <v>13.59</v>
-      </c>
-      <c r="E79" s="1">
-        <v>0.23</v>
-      </c>
-      <c r="F79" t="s">
-        <v>39</v>
-      </c>
-      <c r="G79" s="1">
-        <v>13.59</v>
-      </c>
-      <c r="H79" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>171</v>
-      </c>
-      <c r="B80" t="s">
-        <v>172</v>
-      </c>
-      <c r="C80" s="1">
-        <v>13.79</v>
-      </c>
-      <c r="D80" s="1">
-        <v>13.56</v>
-      </c>
-      <c r="E80" s="1">
-        <v>0.23</v>
-      </c>
-      <c r="F80" t="s">
-        <v>39</v>
-      </c>
-      <c r="G80" s="1">
-        <v>13.56</v>
-      </c>
-      <c r="H80" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>173</v>
-      </c>
-      <c r="B81" t="s">
-        <v>174</v>
-      </c>
-      <c r="C81" s="1">
-        <v>13.79</v>
-      </c>
-      <c r="D81" s="1">
-        <v>13.56</v>
-      </c>
-      <c r="E81" s="1">
-        <v>0.23</v>
-      </c>
-      <c r="F81" t="s">
-        <v>39</v>
-      </c>
-      <c r="G81" s="1">
-        <v>13.56</v>
-      </c>
-      <c r="H81" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>175</v>
-      </c>
-      <c r="B82" t="s">
-        <v>176</v>
-      </c>
-      <c r="C82" s="1">
-        <v>13.79</v>
-      </c>
-      <c r="D82" s="1">
-        <v>13.56</v>
-      </c>
-      <c r="E82" s="1">
-        <v>0.23</v>
-      </c>
-      <c r="F82" t="s">
-        <v>39</v>
-      </c>
-      <c r="G82" s="1">
-        <v>13.56</v>
-      </c>
-      <c r="H82" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>177</v>
-      </c>
-      <c r="B83" t="s">
-        <v>178</v>
-      </c>
-      <c r="C83" s="1">
-        <v>13.81</v>
-      </c>
-      <c r="D83" s="1">
-        <v>13.58</v>
-      </c>
-      <c r="E83" s="1">
-        <v>0.23</v>
-      </c>
-      <c r="F83" t="s">
-        <v>39</v>
-      </c>
-      <c r="G83" s="1">
-        <v>13.58</v>
-      </c>
-      <c r="H83" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>179</v>
-      </c>
-      <c r="B84" t="s">
-        <v>180</v>
-      </c>
-      <c r="C84" s="1">
-        <v>13.81</v>
-      </c>
-      <c r="D84" s="1">
-        <v>13.58</v>
-      </c>
-      <c r="E84" s="1">
-        <v>0.23</v>
-      </c>
-      <c r="F84" t="s">
-        <v>39</v>
-      </c>
-      <c r="G84" s="1">
-        <v>13.58</v>
-      </c>
-      <c r="H84" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>181</v>
-      </c>
-      <c r="B85" t="s">
-        <v>182</v>
-      </c>
-      <c r="C85" s="1">
-        <v>13.79</v>
-      </c>
-      <c r="D85" s="1">
-        <v>13.56</v>
-      </c>
-      <c r="E85" s="1">
-        <v>0.23</v>
-      </c>
-      <c r="F85" t="s">
-        <v>39</v>
-      </c>
-      <c r="G85" s="1">
-        <v>13.56</v>
-      </c>
-      <c r="H85" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>183</v>
-      </c>
-      <c r="B86" t="s">
-        <v>184</v>
-      </c>
-      <c r="C86" s="1">
-        <v>21.99</v>
-      </c>
-      <c r="D86" s="1">
-        <v>21.77</v>
-      </c>
-      <c r="E86" s="1">
-        <v>0.22</v>
-      </c>
-      <c r="F86" t="s">
-        <v>39</v>
-      </c>
-      <c r="G86" s="1">
-        <v>21.77</v>
-      </c>
-      <c r="H86" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>185</v>
-      </c>
-      <c r="B87" t="s">
-        <v>186</v>
-      </c>
-      <c r="C87" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D87" s="1">
-        <v>9.78</v>
-      </c>
-      <c r="E87" s="1">
-        <v>0.21</v>
-      </c>
-      <c r="F87" t="s">
-        <v>187</v>
-      </c>
-      <c r="G87" s="1">
-        <v>9.78</v>
-      </c>
-      <c r="H87" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>188</v>
-      </c>
-      <c r="B88" t="s">
-        <v>189</v>
-      </c>
-      <c r="C88" s="1">
-        <v>13.52</v>
-      </c>
-      <c r="D88" s="1">
-        <v>13.32</v>
-      </c>
-      <c r="E88" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="F88" t="s">
-        <v>39</v>
-      </c>
-      <c r="G88" s="1">
-        <v>13.32</v>
-      </c>
-      <c r="H88" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>190</v>
-      </c>
-      <c r="B89" t="s">
-        <v>191</v>
-      </c>
-      <c r="C89" s="1">
-        <v>21.88</v>
-      </c>
-      <c r="D89" s="1">
-        <v>21.69</v>
-      </c>
-      <c r="E89" s="1">
-        <v>0.19</v>
-      </c>
-      <c r="F89" t="s">
-        <v>39</v>
-      </c>
-      <c r="G89" s="1">
-        <v>21.69</v>
-      </c>
-      <c r="H89" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>192</v>
-      </c>
-      <c r="B90" t="s">
-        <v>193</v>
-      </c>
-      <c r="C90" s="1">
-        <v>13.19</v>
-      </c>
-      <c r="D90" s="1">
-        <v>13</v>
-      </c>
-      <c r="E90" s="1">
-        <v>0.19</v>
-      </c>
-      <c r="F90" t="s">
-        <v>39</v>
-      </c>
-      <c r="G90" s="1">
-        <v>13</v>
-      </c>
-      <c r="H90" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>194</v>
-      </c>
-      <c r="B91" t="s">
-        <v>195</v>
-      </c>
-      <c r="C91" s="1">
-        <v>13.1</v>
-      </c>
-      <c r="D91" s="1">
-        <v>12.93</v>
-      </c>
-      <c r="E91" s="1">
-        <v>0.17</v>
-      </c>
-      <c r="F91" t="s">
-        <v>39</v>
-      </c>
-      <c r="G91" s="1">
-        <v>12.93</v>
-      </c>
-      <c r="H91" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>196</v>
-      </c>
-      <c r="B92" t="s">
-        <v>197</v>
-      </c>
-      <c r="C92" s="1">
-        <v>12.97</v>
-      </c>
-      <c r="D92" s="1">
-        <v>12.82</v>
-      </c>
-      <c r="E92" s="1">
-        <v>0.15</v>
-      </c>
-      <c r="F92" t="s">
-        <v>39</v>
-      </c>
-      <c r="G92" s="1">
-        <v>12.82</v>
-      </c>
-      <c r="H92" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>198</v>
-      </c>
-      <c r="B93" t="s">
-        <v>199</v>
-      </c>
-      <c r="C93" s="1">
-        <v>12.25</v>
-      </c>
-      <c r="D93" s="1">
-        <v>12.14</v>
-      </c>
-      <c r="E93" s="1">
-        <v>0.11</v>
-      </c>
-      <c r="F93" t="s">
-        <v>39</v>
-      </c>
-      <c r="G93" s="1">
-        <v>12.14</v>
-      </c>
-      <c r="H93" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>200</v>
-      </c>
-      <c r="B94" t="s">
-        <v>201</v>
-      </c>
-      <c r="C94" s="1">
-        <v>12.6</v>
-      </c>
-      <c r="D94" s="1">
-        <v>12.49</v>
-      </c>
-      <c r="E94" s="1">
-        <v>0.11</v>
-      </c>
-      <c r="F94" t="s">
-        <v>39</v>
-      </c>
-      <c r="G94" s="1">
-        <v>12.49</v>
-      </c>
-      <c r="H94" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>202</v>
-      </c>
-      <c r="B95" t="s">
-        <v>203</v>
-      </c>
-      <c r="C95" s="1">
-        <v>12.37</v>
-      </c>
-      <c r="D95" s="1">
-        <v>12.28</v>
-      </c>
-      <c r="E95" s="1">
-        <v>0.09</v>
-      </c>
-      <c r="F95" t="s">
-        <v>39</v>
-      </c>
-      <c r="G95" s="1">
-        <v>12.28</v>
-      </c>
-      <c r="H95" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>204</v>
-      </c>
-      <c r="B96" t="s">
-        <v>205</v>
-      </c>
-      <c r="C96" s="1">
-        <v>11.95</v>
-      </c>
-      <c r="D96" s="1">
-        <v>11.89</v>
-      </c>
-      <c r="E96" s="1">
-        <v>0.06</v>
-      </c>
-      <c r="F96" t="s">
-        <v>39</v>
-      </c>
-      <c r="G96" s="1">
-        <v>11.89</v>
-      </c>
-      <c r="H96" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>206</v>
-      </c>
-      <c r="B97" t="s">
-        <v>207</v>
-      </c>
-      <c r="C97" s="1">
-        <v>11.59</v>
-      </c>
-      <c r="D97" s="1">
-        <v>11.54</v>
-      </c>
-      <c r="E97" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="F97" t="s">
-        <v>39</v>
-      </c>
-      <c r="G97" s="1">
-        <v>11.54</v>
-      </c>
-      <c r="H97" t="s">
         <v>11</v>
       </c>
     </row>

--- a/rapporten/prijsrapport-NL-2026-05-17.xlsx
+++ b/rapporten/prijsrapport-NL-2026-05-17.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="157">
   <si>
     <t>Product</t>
   </si>
@@ -134,6 +134,12 @@
   </si>
   <si>
     <t>6291012000261</t>
+  </si>
+  <si>
+    <t>Sentio What Happens Under The Mistletoe Stays Under The Mistletoe - Eau de parfum</t>
+  </si>
+  <si>
+    <t>8721055492795</t>
   </si>
   <si>
     <t>NG Dark Elixir Men Eau de Toilette 100 ml</t>
@@ -867,7 +873,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H71"/>
+  <dimension ref="A1:H72"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -1278,19 +1284,19 @@
         <v>42</v>
       </c>
       <c r="C16" s="1">
-        <v>9.79</v>
+        <v>8.25</v>
       </c>
       <c r="D16" s="1">
-        <v>9.47</v>
+        <v>7.92</v>
       </c>
       <c r="E16" s="1">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="F16" t="s">
         <v>36</v>
       </c>
       <c r="G16" s="1">
-        <v>9.47</v>
+        <v>7.92</v>
       </c>
       <c r="H16" t="s">
         <v>11</v>
@@ -1307,16 +1313,16 @@
         <v>9.79</v>
       </c>
       <c r="D17" s="1">
-        <v>9.5</v>
+        <v>9.47</v>
       </c>
       <c r="E17" s="1">
-        <v>0.29</v>
+        <v>0.32</v>
       </c>
       <c r="F17" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="G17" s="1">
-        <v>9.5</v>
+        <v>9.47</v>
       </c>
       <c r="H17" t="s">
         <v>11</v>
@@ -1356,19 +1362,19 @@
         <v>48</v>
       </c>
       <c r="C19" s="1">
-        <v>14.39</v>
+        <v>9.79</v>
       </c>
       <c r="D19" s="1">
-        <v>14.1</v>
+        <v>9.5</v>
       </c>
       <c r="E19" s="1">
         <v>0.29</v>
       </c>
       <c r="F19" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="G19" s="1">
-        <v>14.1</v>
+        <v>9.5</v>
       </c>
       <c r="H19" t="s">
         <v>11</v>
@@ -1376,25 +1382,25 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" t="s">
         <v>50</v>
       </c>
-      <c r="B20" t="s">
-        <v>51</v>
-      </c>
       <c r="C20" s="1">
-        <v>9.79</v>
+        <v>14.39</v>
       </c>
       <c r="D20" s="1">
-        <v>9.5</v>
+        <v>14.1</v>
       </c>
       <c r="E20" s="1">
         <v>0.29</v>
       </c>
       <c r="F20" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="G20" s="1">
-        <v>9.5</v>
+        <v>14.1</v>
       </c>
       <c r="H20" t="s">
         <v>11</v>
@@ -1928,19 +1934,19 @@
         <v>93</v>
       </c>
       <c r="C41" s="1">
-        <v>14.19</v>
+        <v>9.79</v>
       </c>
       <c r="D41" s="1">
-        <v>13.91</v>
+        <v>9.5</v>
       </c>
       <c r="E41" s="1">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="F41" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="G41" s="1">
-        <v>13.91</v>
+        <v>9.5</v>
       </c>
       <c r="H41" t="s">
         <v>11</v>
@@ -1954,19 +1960,19 @@
         <v>95</v>
       </c>
       <c r="C42" s="1">
-        <v>5.25</v>
+        <v>14.19</v>
       </c>
       <c r="D42" s="1">
-        <v>4.99</v>
+        <v>13.91</v>
       </c>
       <c r="E42" s="1">
-        <v>0.26</v>
+        <v>0.28</v>
       </c>
       <c r="F42" t="s">
-        <v>96</v>
+        <v>51</v>
       </c>
       <c r="G42" s="1">
-        <v>4.99</v>
+        <v>13.91</v>
       </c>
       <c r="H42" t="s">
         <v>11</v>
@@ -1974,10 +1980,10 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>96</v>
+      </c>
+      <c r="B43" t="s">
         <v>97</v>
-      </c>
-      <c r="B43" t="s">
-        <v>98</v>
       </c>
       <c r="C43" s="1">
         <v>5.25</v>
@@ -1989,7 +1995,7 @@
         <v>0.26</v>
       </c>
       <c r="F43" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G43" s="1">
         <v>4.99</v>
@@ -2015,7 +2021,7 @@
         <v>0.26</v>
       </c>
       <c r="F44" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G44" s="1">
         <v>4.99</v>
@@ -2041,7 +2047,7 @@
         <v>0.26</v>
       </c>
       <c r="F45" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G45" s="1">
         <v>4.99</v>
@@ -2067,7 +2073,7 @@
         <v>0.26</v>
       </c>
       <c r="F46" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G46" s="1">
         <v>4.99</v>
@@ -2093,7 +2099,7 @@
         <v>0.26</v>
       </c>
       <c r="F47" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G47" s="1">
         <v>4.99</v>
@@ -2119,7 +2125,7 @@
         <v>0.26</v>
       </c>
       <c r="F48" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G48" s="1">
         <v>4.99</v>
@@ -2145,7 +2151,7 @@
         <v>0.26</v>
       </c>
       <c r="F49" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G49" s="1">
         <v>4.99</v>
@@ -2171,7 +2177,7 @@
         <v>0.26</v>
       </c>
       <c r="F50" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G50" s="1">
         <v>4.99</v>
@@ -2197,7 +2203,7 @@
         <v>0.26</v>
       </c>
       <c r="F51" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G51" s="1">
         <v>4.99</v>
@@ -2223,7 +2229,7 @@
         <v>0.26</v>
       </c>
       <c r="F52" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G52" s="1">
         <v>4.99</v>
@@ -2249,7 +2255,7 @@
         <v>0.26</v>
       </c>
       <c r="F53" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G53" s="1">
         <v>4.99</v>
@@ -2275,7 +2281,7 @@
         <v>0.26</v>
       </c>
       <c r="F54" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G54" s="1">
         <v>4.99</v>
@@ -2301,7 +2307,7 @@
         <v>0.26</v>
       </c>
       <c r="F55" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G55" s="1">
         <v>4.99</v>
@@ -2327,7 +2333,7 @@
         <v>0.26</v>
       </c>
       <c r="F56" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G56" s="1">
         <v>4.99</v>
@@ -2353,7 +2359,7 @@
         <v>0.26</v>
       </c>
       <c r="F57" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G57" s="1">
         <v>4.99</v>
@@ -2379,7 +2385,7 @@
         <v>0.26</v>
       </c>
       <c r="F58" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G58" s="1">
         <v>4.99</v>
@@ -2405,7 +2411,7 @@
         <v>0.26</v>
       </c>
       <c r="F59" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G59" s="1">
         <v>4.99</v>
@@ -2431,7 +2437,7 @@
         <v>0.26</v>
       </c>
       <c r="F60" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G60" s="1">
         <v>4.99</v>
@@ -2457,7 +2463,7 @@
         <v>0.26</v>
       </c>
       <c r="F61" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G61" s="1">
         <v>4.99</v>
@@ -2483,7 +2489,7 @@
         <v>0.26</v>
       </c>
       <c r="F62" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G62" s="1">
         <v>4.99</v>
@@ -2500,19 +2506,19 @@
         <v>138</v>
       </c>
       <c r="C63" s="1">
-        <v>13.86</v>
+        <v>5.25</v>
       </c>
       <c r="D63" s="1">
-        <v>13.62</v>
+        <v>4.99</v>
       </c>
       <c r="E63" s="1">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="F63" t="s">
-        <v>49</v>
+        <v>98</v>
       </c>
       <c r="G63" s="1">
-        <v>13.62</v>
+        <v>4.99</v>
       </c>
       <c r="H63" t="s">
         <v>11</v>
@@ -2526,19 +2532,19 @@
         <v>140</v>
       </c>
       <c r="C64" s="1">
-        <v>13.89</v>
+        <v>13.86</v>
       </c>
       <c r="D64" s="1">
-        <v>13.65</v>
+        <v>13.62</v>
       </c>
       <c r="E64" s="1">
         <v>0.24</v>
       </c>
       <c r="F64" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G64" s="1">
-        <v>13.65</v>
+        <v>13.62</v>
       </c>
       <c r="H64" t="s">
         <v>11</v>
@@ -2552,19 +2558,19 @@
         <v>142</v>
       </c>
       <c r="C65" s="1">
-        <v>13.78</v>
+        <v>13.89</v>
       </c>
       <c r="D65" s="1">
-        <v>13.55</v>
+        <v>13.65</v>
       </c>
       <c r="E65" s="1">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="F65" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G65" s="1">
-        <v>13.55</v>
+        <v>13.65</v>
       </c>
       <c r="H65" t="s">
         <v>11</v>
@@ -2578,19 +2584,19 @@
         <v>144</v>
       </c>
       <c r="C66" s="1">
-        <v>13.82</v>
+        <v>13.78</v>
       </c>
       <c r="D66" s="1">
-        <v>13.59</v>
+        <v>13.55</v>
       </c>
       <c r="E66" s="1">
         <v>0.23</v>
       </c>
       <c r="F66" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G66" s="1">
-        <v>13.59</v>
+        <v>13.55</v>
       </c>
       <c r="H66" t="s">
         <v>11</v>
@@ -2604,19 +2610,19 @@
         <v>146</v>
       </c>
       <c r="C67" s="1">
-        <v>13.78</v>
+        <v>13.82</v>
       </c>
       <c r="D67" s="1">
-        <v>13.55</v>
+        <v>13.59</v>
       </c>
       <c r="E67" s="1">
         <v>0.23</v>
       </c>
       <c r="F67" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G67" s="1">
-        <v>13.55</v>
+        <v>13.59</v>
       </c>
       <c r="H67" t="s">
         <v>11</v>
@@ -2630,19 +2636,19 @@
         <v>148</v>
       </c>
       <c r="C68" s="1">
-        <v>13.75</v>
+        <v>13.78</v>
       </c>
       <c r="D68" s="1">
-        <v>13.52</v>
+        <v>13.55</v>
       </c>
       <c r="E68" s="1">
         <v>0.23</v>
       </c>
       <c r="F68" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G68" s="1">
-        <v>13.52</v>
+        <v>13.55</v>
       </c>
       <c r="H68" t="s">
         <v>11</v>
@@ -2656,19 +2662,19 @@
         <v>150</v>
       </c>
       <c r="C69" s="1">
-        <v>12.87</v>
+        <v>13.75</v>
       </c>
       <c r="D69" s="1">
-        <v>12.73</v>
+        <v>13.52</v>
       </c>
       <c r="E69" s="1">
-        <v>0.14</v>
+        <v>0.23</v>
       </c>
       <c r="F69" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G69" s="1">
-        <v>12.73</v>
+        <v>13.52</v>
       </c>
       <c r="H69" t="s">
         <v>11</v>
@@ -2682,19 +2688,19 @@
         <v>152</v>
       </c>
       <c r="C70" s="1">
-        <v>12.35</v>
+        <v>12.87</v>
       </c>
       <c r="D70" s="1">
-        <v>12.26</v>
+        <v>12.73</v>
       </c>
       <c r="E70" s="1">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="F70" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G70" s="1">
-        <v>12.26</v>
+        <v>12.73</v>
       </c>
       <c r="H70" t="s">
         <v>11</v>
@@ -2708,21 +2714,47 @@
         <v>154</v>
       </c>
       <c r="C71" s="1">
-        <v>12.45</v>
+        <v>12.35</v>
       </c>
       <c r="D71" s="1">
-        <v>12.36</v>
+        <v>12.26</v>
       </c>
       <c r="E71" s="1">
         <v>0.09</v>
       </c>
       <c r="F71" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G71" s="1">
+        <v>12.26</v>
+      </c>
+      <c r="H71" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>155</v>
+      </c>
+      <c r="B72" t="s">
+        <v>156</v>
+      </c>
+      <c r="C72" s="1">
+        <v>12.45</v>
+      </c>
+      <c r="D72" s="1">
         <v>12.36</v>
       </c>
-      <c r="H71" t="s">
+      <c r="E72" s="1">
+        <v>0.09</v>
+      </c>
+      <c r="F72" t="s">
+        <v>51</v>
+      </c>
+      <c r="G72" s="1">
+        <v>12.36</v>
+      </c>
+      <c r="H72" t="s">
         <v>11</v>
       </c>
     </row>

--- a/rapporten/prijsrapport-NL-2026-05-17.xlsx
+++ b/rapporten/prijsrapport-NL-2026-05-17.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="157">
   <si>
     <t>Product</t>
   </si>
@@ -55,6 +55,9 @@
     <t>8715658370260</t>
   </si>
   <si>
+    <t>Koopjesfun.nl</t>
+  </si>
+  <si>
     <t>Colorful Shoe Shoe Pack</t>
   </si>
   <si>
@@ -164,9 +167,6 @@
   </si>
   <si>
     <t>6291012005082</t>
-  </si>
-  <si>
-    <t>Koopjesfun.nl</t>
   </si>
   <si>
     <t>Omerta - Big Release The Mood - EDT men - 100ml</t>
@@ -873,7 +873,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H72"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -966,25 +966,25 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="1">
+        <v>11.5</v>
+      </c>
+      <c r="D4" s="1">
+        <v>9.99</v>
+      </c>
+      <c r="E4" s="1">
+        <v>1.51</v>
+      </c>
+      <c r="F4" t="s">
         <v>14</v>
       </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="1">
-        <v>17.45</v>
-      </c>
-      <c r="D4" s="1">
-        <v>15.95</v>
-      </c>
-      <c r="E4" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="F4" t="s">
-        <v>16</v>
-      </c>
       <c r="G4" s="1">
-        <v>15.95</v>
+        <v>11.5</v>
       </c>
       <c r="H4" t="s">
         <v>11</v>
@@ -992,22 +992,22 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C5" s="1">
-        <v>16.95</v>
+        <v>17.45</v>
       </c>
       <c r="D5" s="1">
         <v>15.95</v>
       </c>
       <c r="E5" s="1">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G5" s="1">
         <v>15.95</v>
@@ -1018,10 +1018,10 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
         <v>19</v>
-      </c>
-      <c r="B6" t="s">
-        <v>20</v>
       </c>
       <c r="C6" s="1">
         <v>16.95</v>
@@ -1033,7 +1033,7 @@
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G6" s="1">
         <v>15.95</v>
@@ -1044,10 +1044,10 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" t="s">
         <v>21</v>
-      </c>
-      <c r="B7" t="s">
-        <v>22</v>
       </c>
       <c r="C7" s="1">
         <v>16.95</v>
@@ -1059,7 +1059,7 @@
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G7" s="1">
         <v>15.95</v>
@@ -1070,10 +1070,10 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" t="s">
         <v>23</v>
-      </c>
-      <c r="B8" t="s">
-        <v>24</v>
       </c>
       <c r="C8" s="1">
         <v>16.95</v>
@@ -1085,7 +1085,7 @@
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G8" s="1">
         <v>15.95</v>
@@ -1096,10 +1096,10 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" t="s">
         <v>25</v>
-      </c>
-      <c r="B9" t="s">
-        <v>26</v>
       </c>
       <c r="C9" s="1">
         <v>16.95</v>
@@ -1111,7 +1111,7 @@
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G9" s="1">
         <v>15.95</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" t="s">
         <v>27</v>
-      </c>
-      <c r="B10" t="s">
-        <v>28</v>
       </c>
       <c r="C10" s="1">
         <v>16.95</v>
@@ -1137,7 +1137,7 @@
         <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G10" s="1">
         <v>15.95</v>
@@ -1148,22 +1148,22 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" t="s">
         <v>29</v>
       </c>
-      <c r="B11" t="s">
-        <v>30</v>
-      </c>
       <c r="C11" s="1">
-        <v>16.89</v>
+        <v>16.95</v>
       </c>
       <c r="D11" s="1">
         <v>15.95</v>
       </c>
       <c r="E11" s="1">
-        <v>0.94</v>
+        <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G11" s="1">
         <v>15.95</v>
@@ -1174,25 +1174,25 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" t="s">
         <v>31</v>
       </c>
-      <c r="B12" t="s">
-        <v>32</v>
-      </c>
       <c r="C12" s="1">
-        <v>9.94</v>
+        <v>16.89</v>
       </c>
       <c r="D12" s="1">
-        <v>9.48</v>
+        <v>15.95</v>
       </c>
       <c r="E12" s="1">
-        <v>0.46</v>
+        <v>0.94</v>
       </c>
       <c r="F12" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="G12" s="1">
-        <v>9.48</v>
+        <v>15.95</v>
       </c>
       <c r="H12" t="s">
         <v>11</v>
@@ -1200,25 +1200,25 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="1">
+        <v>9.94</v>
+      </c>
+      <c r="D13" s="1">
+        <v>9.48</v>
+      </c>
+      <c r="E13" s="1">
+        <v>0.46</v>
+      </c>
+      <c r="F13" t="s">
         <v>34</v>
       </c>
-      <c r="B13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" s="1">
-        <v>14.05</v>
-      </c>
-      <c r="D13" s="1">
-        <v>13.66</v>
-      </c>
-      <c r="E13" s="1">
-        <v>0.39</v>
-      </c>
-      <c r="F13" t="s">
-        <v>36</v>
-      </c>
       <c r="G13" s="1">
-        <v>13.66</v>
+        <v>9.48</v>
       </c>
       <c r="H13" t="s">
         <v>11</v>
@@ -1226,25 +1226,25 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="1">
+        <v>14.05</v>
+      </c>
+      <c r="D14" s="1">
+        <v>13.66</v>
+      </c>
+      <c r="E14" s="1">
+        <v>0.39</v>
+      </c>
+      <c r="F14" t="s">
         <v>37</v>
       </c>
-      <c r="B14" t="s">
-        <v>38</v>
-      </c>
-      <c r="C14" s="1">
-        <v>14.25</v>
-      </c>
-      <c r="D14" s="1">
-        <v>13.91</v>
-      </c>
-      <c r="E14" s="1">
-        <v>0.34</v>
-      </c>
-      <c r="F14" t="s">
-        <v>36</v>
-      </c>
       <c r="G14" s="1">
-        <v>13.91</v>
+        <v>13.66</v>
       </c>
       <c r="H14" t="s">
         <v>11</v>
@@ -1252,25 +1252,25 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" t="s">
         <v>39</v>
       </c>
-      <c r="B15" t="s">
-        <v>40</v>
-      </c>
       <c r="C15" s="1">
-        <v>9.79</v>
+        <v>14.25</v>
       </c>
       <c r="D15" s="1">
-        <v>9.45</v>
+        <v>13.91</v>
       </c>
       <c r="E15" s="1">
         <v>0.34</v>
       </c>
       <c r="F15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G15" s="1">
-        <v>9.45</v>
+        <v>13.91</v>
       </c>
       <c r="H15" t="s">
         <v>11</v>
@@ -1278,25 +1278,25 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" t="s">
         <v>41</v>
       </c>
-      <c r="B16" t="s">
-        <v>42</v>
-      </c>
       <c r="C16" s="1">
-        <v>8.25</v>
+        <v>9.79</v>
       </c>
       <c r="D16" s="1">
-        <v>7.92</v>
+        <v>9.45</v>
       </c>
       <c r="E16" s="1">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="F16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G16" s="1">
-        <v>7.92</v>
+        <v>9.45</v>
       </c>
       <c r="H16" t="s">
         <v>11</v>
@@ -1304,25 +1304,25 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" t="s">
         <v>43</v>
       </c>
-      <c r="B17" t="s">
-        <v>44</v>
-      </c>
       <c r="C17" s="1">
-        <v>9.79</v>
+        <v>8.25</v>
       </c>
       <c r="D17" s="1">
-        <v>9.47</v>
+        <v>7.92</v>
       </c>
       <c r="E17" s="1">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="F17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G17" s="1">
-        <v>9.47</v>
+        <v>7.92</v>
       </c>
       <c r="H17" t="s">
         <v>11</v>
@@ -1330,25 +1330,25 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" t="s">
         <v>45</v>
-      </c>
-      <c r="B18" t="s">
-        <v>46</v>
       </c>
       <c r="C18" s="1">
         <v>9.79</v>
       </c>
       <c r="D18" s="1">
-        <v>9.5</v>
+        <v>9.47</v>
       </c>
       <c r="E18" s="1">
-        <v>0.29</v>
+        <v>0.32</v>
       </c>
       <c r="F18" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="G18" s="1">
-        <v>9.5</v>
+        <v>9.47</v>
       </c>
       <c r="H18" t="s">
         <v>11</v>
@@ -1356,10 +1356,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" t="s">
         <v>47</v>
-      </c>
-      <c r="B19" t="s">
-        <v>48</v>
       </c>
       <c r="C19" s="1">
         <v>9.79</v>
@@ -1371,7 +1371,7 @@
         <v>0.29</v>
       </c>
       <c r="F19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G19" s="1">
         <v>9.5</v>
@@ -1382,25 +1382,25 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" t="s">
         <v>49</v>
       </c>
-      <c r="B20" t="s">
-        <v>50</v>
-      </c>
       <c r="C20" s="1">
-        <v>14.39</v>
+        <v>9.79</v>
       </c>
       <c r="D20" s="1">
-        <v>14.1</v>
+        <v>9.5</v>
       </c>
       <c r="E20" s="1">
         <v>0.29</v>
       </c>
       <c r="F20" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="G20" s="1">
-        <v>14.1</v>
+        <v>9.5</v>
       </c>
       <c r="H20" t="s">
         <v>11</v>
@@ -1408,25 +1408,25 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B21" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C21" s="1">
-        <v>9.79</v>
+        <v>14.39</v>
       </c>
       <c r="D21" s="1">
-        <v>9.5</v>
+        <v>14.1</v>
       </c>
       <c r="E21" s="1">
         <v>0.29</v>
       </c>
       <c r="F21" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G21" s="1">
-        <v>9.5</v>
+        <v>14.1</v>
       </c>
       <c r="H21" t="s">
         <v>11</v>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B22" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C22" s="1">
         <v>9.79</v>
@@ -1449,7 +1449,7 @@
         <v>0.29</v>
       </c>
       <c r="F22" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G22" s="1">
         <v>9.5</v>
@@ -1460,10 +1460,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B23" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C23" s="1">
         <v>9.79</v>
@@ -1475,7 +1475,7 @@
         <v>0.29</v>
       </c>
       <c r="F23" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G23" s="1">
         <v>9.5</v>
@@ -1486,10 +1486,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B24" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C24" s="1">
         <v>9.79</v>
@@ -1501,7 +1501,7 @@
         <v>0.29</v>
       </c>
       <c r="F24" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G24" s="1">
         <v>9.5</v>
@@ -1512,10 +1512,10 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B25" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C25" s="1">
         <v>9.79</v>
@@ -1527,7 +1527,7 @@
         <v>0.29</v>
       </c>
       <c r="F25" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G25" s="1">
         <v>9.5</v>
@@ -1538,10 +1538,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B26" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C26" s="1">
         <v>9.79</v>
@@ -1553,7 +1553,7 @@
         <v>0.29</v>
       </c>
       <c r="F26" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G26" s="1">
         <v>9.5</v>
@@ -1564,10 +1564,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B27" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C27" s="1">
         <v>9.79</v>
@@ -1579,7 +1579,7 @@
         <v>0.29</v>
       </c>
       <c r="F27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G27" s="1">
         <v>9.5</v>
@@ -1590,10 +1590,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B28" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C28" s="1">
         <v>9.79</v>
@@ -1605,7 +1605,7 @@
         <v>0.29</v>
       </c>
       <c r="F28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G28" s="1">
         <v>9.5</v>
@@ -1616,10 +1616,10 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B29" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C29" s="1">
         <v>9.79</v>
@@ -1631,7 +1631,7 @@
         <v>0.29</v>
       </c>
       <c r="F29" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G29" s="1">
         <v>9.5</v>
@@ -1642,10 +1642,10 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B30" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C30" s="1">
         <v>9.79</v>
@@ -1657,7 +1657,7 @@
         <v>0.29</v>
       </c>
       <c r="F30" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G30" s="1">
         <v>9.5</v>
@@ -1668,10 +1668,10 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B31" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C31" s="1">
         <v>9.79</v>
@@ -1683,7 +1683,7 @@
         <v>0.29</v>
       </c>
       <c r="F31" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G31" s="1">
         <v>9.5</v>
@@ -1694,10 +1694,10 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B32" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C32" s="1">
         <v>9.79</v>
@@ -1709,7 +1709,7 @@
         <v>0.29</v>
       </c>
       <c r="F32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G32" s="1">
         <v>9.5</v>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B33" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C33" s="1">
         <v>9.79</v>
@@ -1735,7 +1735,7 @@
         <v>0.29</v>
       </c>
       <c r="F33" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G33" s="1">
         <v>9.5</v>
@@ -1746,10 +1746,10 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B34" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C34" s="1">
         <v>9.79</v>
@@ -1761,7 +1761,7 @@
         <v>0.29</v>
       </c>
       <c r="F34" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G34" s="1">
         <v>9.5</v>
@@ -1772,10 +1772,10 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B35" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C35" s="1">
         <v>9.79</v>
@@ -1787,7 +1787,7 @@
         <v>0.29</v>
       </c>
       <c r="F35" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G35" s="1">
         <v>9.5</v>
@@ -1798,10 +1798,10 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B36" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C36" s="1">
         <v>9.79</v>
@@ -1813,7 +1813,7 @@
         <v>0.29</v>
       </c>
       <c r="F36" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G36" s="1">
         <v>9.5</v>
@@ -1824,10 +1824,10 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B37" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C37" s="1">
         <v>9.79</v>
@@ -1839,7 +1839,7 @@
         <v>0.29</v>
       </c>
       <c r="F37" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G37" s="1">
         <v>9.5</v>
@@ -1850,10 +1850,10 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B38" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C38" s="1">
         <v>9.79</v>
@@ -1865,7 +1865,7 @@
         <v>0.29</v>
       </c>
       <c r="F38" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G38" s="1">
         <v>9.5</v>
@@ -1876,10 +1876,10 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B39" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C39" s="1">
         <v>9.79</v>
@@ -1891,7 +1891,7 @@
         <v>0.29</v>
       </c>
       <c r="F39" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G39" s="1">
         <v>9.5</v>
@@ -1902,10 +1902,10 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B40" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C40" s="1">
         <v>9.79</v>
@@ -1917,7 +1917,7 @@
         <v>0.29</v>
       </c>
       <c r="F40" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G40" s="1">
         <v>9.5</v>
@@ -1928,10 +1928,10 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B41" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C41" s="1">
         <v>9.79</v>
@@ -1943,7 +1943,7 @@
         <v>0.29</v>
       </c>
       <c r="F41" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G41" s="1">
         <v>9.5</v>
@@ -1954,25 +1954,25 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B42" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C42" s="1">
-        <v>14.19</v>
+        <v>9.79</v>
       </c>
       <c r="D42" s="1">
-        <v>13.91</v>
+        <v>9.5</v>
       </c>
       <c r="E42" s="1">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="F42" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="G42" s="1">
-        <v>13.91</v>
+        <v>9.5</v>
       </c>
       <c r="H42" t="s">
         <v>11</v>
@@ -1980,25 +1980,25 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B43" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C43" s="1">
-        <v>5.25</v>
+        <v>14.19</v>
       </c>
       <c r="D43" s="1">
-        <v>4.99</v>
+        <v>13.91</v>
       </c>
       <c r="E43" s="1">
-        <v>0.26</v>
+        <v>0.28</v>
       </c>
       <c r="F43" t="s">
-        <v>98</v>
+        <v>14</v>
       </c>
       <c r="G43" s="1">
-        <v>4.99</v>
+        <v>13.91</v>
       </c>
       <c r="H43" t="s">
         <v>11</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B44" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C44" s="1">
         <v>5.25</v>
@@ -2032,10 +2032,10 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B45" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C45" s="1">
         <v>5.25</v>
@@ -2058,10 +2058,10 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B46" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C46" s="1">
         <v>5.25</v>
@@ -2084,10 +2084,10 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B47" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C47" s="1">
         <v>5.25</v>
@@ -2110,10 +2110,10 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B48" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C48" s="1">
         <v>5.25</v>
@@ -2136,10 +2136,10 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B49" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C49" s="1">
         <v>5.25</v>
@@ -2162,10 +2162,10 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B50" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C50" s="1">
         <v>5.25</v>
@@ -2188,10 +2188,10 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B51" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C51" s="1">
         <v>5.25</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B52" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C52" s="1">
         <v>5.25</v>
@@ -2240,10 +2240,10 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B53" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C53" s="1">
         <v>5.25</v>
@@ -2266,10 +2266,10 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B54" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C54" s="1">
         <v>5.25</v>
@@ -2292,10 +2292,10 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B55" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C55" s="1">
         <v>5.25</v>
@@ -2318,10 +2318,10 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B56" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C56" s="1">
         <v>5.25</v>
@@ -2344,10 +2344,10 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B57" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C57" s="1">
         <v>5.25</v>
@@ -2370,10 +2370,10 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B58" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C58" s="1">
         <v>5.25</v>
@@ -2396,10 +2396,10 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B59" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C59" s="1">
         <v>5.25</v>
@@ -2422,10 +2422,10 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B60" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C60" s="1">
         <v>5.25</v>
@@ -2448,10 +2448,10 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B61" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C61" s="1">
         <v>5.25</v>
@@ -2474,10 +2474,10 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B62" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C62" s="1">
         <v>5.25</v>
@@ -2500,10 +2500,10 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B63" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C63" s="1">
         <v>5.25</v>
@@ -2526,25 +2526,25 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B64" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C64" s="1">
-        <v>13.86</v>
+        <v>5.25</v>
       </c>
       <c r="D64" s="1">
-        <v>13.62</v>
+        <v>4.99</v>
       </c>
       <c r="E64" s="1">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="F64" t="s">
-        <v>51</v>
+        <v>98</v>
       </c>
       <c r="G64" s="1">
-        <v>13.62</v>
+        <v>4.99</v>
       </c>
       <c r="H64" t="s">
         <v>11</v>
@@ -2552,25 +2552,25 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B65" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C65" s="1">
-        <v>13.89</v>
+        <v>13.86</v>
       </c>
       <c r="D65" s="1">
-        <v>13.65</v>
+        <v>13.62</v>
       </c>
       <c r="E65" s="1">
         <v>0.24</v>
       </c>
       <c r="F65" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="G65" s="1">
-        <v>13.65</v>
+        <v>13.62</v>
       </c>
       <c r="H65" t="s">
         <v>11</v>
@@ -2578,25 +2578,25 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B66" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C66" s="1">
-        <v>13.78</v>
+        <v>13.89</v>
       </c>
       <c r="D66" s="1">
-        <v>13.55</v>
+        <v>13.65</v>
       </c>
       <c r="E66" s="1">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="F66" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="G66" s="1">
-        <v>13.55</v>
+        <v>13.65</v>
       </c>
       <c r="H66" t="s">
         <v>11</v>
@@ -2604,25 +2604,25 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B67" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C67" s="1">
-        <v>13.82</v>
+        <v>13.78</v>
       </c>
       <c r="D67" s="1">
-        <v>13.59</v>
+        <v>13.55</v>
       </c>
       <c r="E67" s="1">
         <v>0.23</v>
       </c>
       <c r="F67" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="G67" s="1">
-        <v>13.59</v>
+        <v>13.55</v>
       </c>
       <c r="H67" t="s">
         <v>11</v>
@@ -2630,25 +2630,25 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B68" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C68" s="1">
-        <v>13.78</v>
+        <v>13.82</v>
       </c>
       <c r="D68" s="1">
-        <v>13.55</v>
+        <v>13.59</v>
       </c>
       <c r="E68" s="1">
         <v>0.23</v>
       </c>
       <c r="F68" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="G68" s="1">
-        <v>13.55</v>
+        <v>13.59</v>
       </c>
       <c r="H68" t="s">
         <v>11</v>
@@ -2656,25 +2656,25 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B69" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C69" s="1">
-        <v>13.75</v>
+        <v>13.78</v>
       </c>
       <c r="D69" s="1">
-        <v>13.52</v>
+        <v>13.55</v>
       </c>
       <c r="E69" s="1">
         <v>0.23</v>
       </c>
       <c r="F69" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="G69" s="1">
-        <v>13.52</v>
+        <v>13.55</v>
       </c>
       <c r="H69" t="s">
         <v>11</v>
@@ -2682,25 +2682,25 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B70" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C70" s="1">
-        <v>12.87</v>
+        <v>13.75</v>
       </c>
       <c r="D70" s="1">
-        <v>12.73</v>
+        <v>13.52</v>
       </c>
       <c r="E70" s="1">
-        <v>0.14</v>
+        <v>0.23</v>
       </c>
       <c r="F70" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="G70" s="1">
-        <v>12.73</v>
+        <v>13.52</v>
       </c>
       <c r="H70" t="s">
         <v>11</v>
@@ -2708,25 +2708,25 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B71" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C71" s="1">
-        <v>12.35</v>
+        <v>12.87</v>
       </c>
       <c r="D71" s="1">
-        <v>12.26</v>
+        <v>12.73</v>
       </c>
       <c r="E71" s="1">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="F71" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="G71" s="1">
-        <v>12.26</v>
+        <v>12.73</v>
       </c>
       <c r="H71" t="s">
         <v>11</v>
@@ -2734,27 +2734,53 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B72" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C72" s="1">
-        <v>12.45</v>
+        <v>12.35</v>
       </c>
       <c r="D72" s="1">
-        <v>12.36</v>
+        <v>12.26</v>
       </c>
       <c r="E72" s="1">
         <v>0.09</v>
       </c>
       <c r="F72" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="G72" s="1">
+        <v>12.26</v>
+      </c>
+      <c r="H72" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>155</v>
+      </c>
+      <c r="B73" t="s">
+        <v>156</v>
+      </c>
+      <c r="C73" s="1">
+        <v>12.45</v>
+      </c>
+      <c r="D73" s="1">
         <v>12.36</v>
       </c>
-      <c r="H72" t="s">
+      <c r="E73" s="1">
+        <v>0.09</v>
+      </c>
+      <c r="F73" t="s">
+        <v>14</v>
+      </c>
+      <c r="G73" s="1">
+        <v>12.36</v>
+      </c>
+      <c r="H73" t="s">
         <v>11</v>
       </c>
     </row>
